--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_06_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_06_18_Cau.xlsx
@@ -715,7 +715,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một trường hợp không gắn với bằng chứng sẽ không giúp xác định lỗi hồi quy nằm ở retrieval hay generation.</t>
+          <t>Để xây dựng một trường hợp kiểm thử hồi quy RAG (regression test fixture) có thể tái lập từ log sự cố, bản ghi kiểm thử bắt buộc phải có: (a) Câu hỏi đầu vào; (b) Đáp án chuẩn hoặc phạm vi đáp án cho phép; (c) Nguồn tài liệu hoặc chunk evidence kỳ vọng; (d) Khả năng trả lời (answerability label); (e) Độ khó và phân loại lỗi; (f) Định danh người đánh giá và phiên bản kiểm thử.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tồn tại và hỗ trợ là hai điều kiện độc lập.</t>
+          <t>Khi mệnh đề trích dẫn [D3] nhưng đoạn trích D3 không nêu con số mà mệnh đề khẳng định, trong khi D4 lại chứa con số đó: (a) Loại bỏ D3 vì không hỗ trợ dữ kiện con số; (b) Dùng D4 nếu D4 thực sự hỗ trợ đầy đủ mệnh đề; (c) Đặt citation gắn liền ngay mệnh đề nguyên tử chứa con số; (e) Nếu không có tài liệu nào hỗ trợ thì phải sửa, bỏ hoặc từ chối trả lời (abstain) ở mệnh đề đó. Tuyệt đối không giữ D3 chỉ vì ID có tồn tại.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_06_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_06_18_Cau.xlsx
@@ -624,10 +624,27 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Lập tập dữ kiện bắt buộc rồi đánh dấu dữ kiện nào có hoặc vắng mặt trong câu trả lời.
-Phân tích theo nguyên lý thiết kế: Lập tập dữ kiện bắt buộc rồi đánh dấu dữ kiện nào có hoặc vắng mặt trong câu trả lời.</t>
+- [Tính đúng Answer Completeness = 2/3] (1.5 điểm): Tính chính xác tỷ lệ 2/3 = 0.67 (66.7%) do bỏ sót dữ kiện ngoại lệ.
+- [Phân biệt rạch ròi 2 trường hợp bản chất] (2.0 điểm): Phân biệt rõ ràng lỗi do Generator đọc sót khi context đã có sẵn vs lỗi Retrieval không tìm ra tài liệu.
+- [Định hướng giải pháp đúng tầng] (0.5 điểm): Xác định hướng khắc phục ở prompt/generation chứ không đổi thuật toán retrieval.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Độ đầy đủ của câu trả lời (Answer Completeness Computation):
+- Công thức Độ đầy đủ: `Answer Completeness = (Số dữ kiện bắt buộc có trong câu trả lời) / (Tổng số dữ kiện bắt buộc mà Context hỗ trợ)`.
+- Phân tích dữ kiện:
+  + Tập dữ kiện bắt buộc được Context hỗ trợ đầy đủ: `{Hạn chót, Người phê duyệt, Ngoại lệ}` (Tổng số = 3 dữ kiện).
+  + Tập dữ kiện xuất hiện trong câu trả lời: `{Hạn chót, Người phê duyệt}` (Số lượng xuất hiện = 2 dữ kiện).
+- **Tính toán điểm số**: `Answer Completeness = 2 / 3 = 0.67` (hoặc 66.7%).
+2. Phân biệt rạch ròi với trường hợp Retrieval không tìm thấy bằng chứng:
+- **Trường hợp hiện tại (Generation Omission Defect / Lỗi Bỏ sót ở Tầng Tạo sinh)**:
+  + Bằng chứng về 'Ngoại lệ' **HOÀN TOÀN CÓ MẶT VÀ NẰM TRONG CONTEXT** được gửi tới mô hình. Tầng retrieval đã hoàn thành xuất sắc nhiệm vụ.
+  + Lỗi xảy ra hoàn toàn do LLM đọc sót thông tin hoặc bị giới hạn bởi độ dài phản hồi, tự ý bỏ qua dữ kiện ngoại lệ khi tổng hợp câu trả lời.
+- **Trường hợp Retrieval không tìm thấy bằng chứng (Retrieval Recall Failure)**:
+  + Context được gửi tới LLM hoàn toàn **KHÔNG CÓ ĐOẠN NÀO NHẮC ĐẾN NGOẠI LỆ**.
+  + Trong trường hợp đó, LLM không trả lời về ngoại lệ là do không có dữ liệu đầu vào (không thể trách LLM, lỗi thuộc về tầng retrieval).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Cần phân định rạch ròi giữa 'Retrieval bỏ sót bằng chứng' và 'LLM bỏ sót dữ kiện khi tổng hợp'. Khi ngữ cảnh đã có sẵn dữ kiện nhưng câu trả lời lại thiếu, giải pháp phải là tinh chỉnh System Prompt yêu cầu liệt kê đầy đủ ngoại lệ hoặc chia nhỏ câu hỏi, chứ không phải đi thay đổi thuật toán tìm kiếm vector.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ragas Documentation: 'Answer Semantic Similarity and Completeness' &amp; TruLens QA Evaluation</t>
         </is>
       </c>
     </row>
@@ -658,10 +675,25 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Lập tập dữ kiện bắt buộc rồi đánh dấu dữ kiện nào có hoặc vắng mặt trong câu trả lời.
-Phân tích theo nguyên lý thiết kế: Lập tập dữ kiện bắt buộc rồi đánh dấu dữ kiện nào có hoặc vắng mặt trong câu trả lời.</t>
+- [Đánh giá Completeness đạt tối đa 1.0 có căn cứ] (1.5 điểm): Khẳng định câu trả lời đạt điểm tối đa trên phạm vi bằng chứng được hỗ trợ (2/2 vế).
+- [Cấm phạt hành vi Abstain đúng đắn] (1.5 điểm): Phân tích sâu sắc: việc phạt sẽ tạo động lực xấu ép mô hình tự bịa đặt thông tin để lấy điểm.
+- [Đề xuất công thức Grounded Completeness] (1.0 điểm): Chuẩn hóa mẫu số chỉ tính trên các dữ kiện mà corpus thực sự hỗ trợ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Độ đầy đủ có nguyên tắc (Principled Completeness Assessment):
+- Phân tích tình huống:
+  + Câu hỏi có 3 vế: `{Vế 1, Vế 2, Vế 3}`.
+  + Kho ngữ liệu (Corpus) và Context chỉ có bằng chứng cho 2 vế `{Vế 1, Vế 2}`, hoàn toàn không có thông tin cho `{Vế 3}`.
+  + Câu trả lời đã trả lời đầy đủ, chính xác 2 vế đầu và **tuyên bố từ chối trả lời (Abstain) có căn cứ ở vế thứ 3**.
+- **Đánh giá điểm số**: Câu trả lời phải được chấm **ĐỘ ĐẦY ĐỦ TUYỆT ĐỐI (Completeness = 1.0 / 100%) TRÊN PHẠM VI BẰNG CHỨNG ĐƯỢC HỖ TRỢ (Corpus-Grounded Completeness)**.
+2. Biện minh vì sao TUYỆT ĐỐI KHÔNG ĐƯỢC PHẠT câu trả lời:
+- Nếu phạt câu trả lời vì không trả lời vế thứ 3, hệ thống vô tình tạo ra một động lực tiêu cực cực kỳ nguy hiểm (Perverse Incentive): Ép buộc mô hình ngôn ngữ phải tự bịa đặt dữ kiện (Hallucinate) ở vế thứ 3 để đạt điểm độ đầy đủ tối đa!
+- Hành vi trả lời những gì có bằng chứng và thẳng thắn tuyên bố không có thông tin cho phần corpus không hỗ trợ là **HÀNH VI CHUẨN MỰC CAO NHẤT CỦA MỘT HỆ THỐNG RAG TIN CẬY** (Trustworthy &amp; Faithful AI).
+3. Công thức đánh giá chuẩn hóa:
+`Grounded Completeness = (Dữ kiện trả lời đúng) / (Dữ kiện bắt buộc ĐƯỢC CORPUS HỖ TRỢ) = 2 / 2 = 1.0`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một hệ thống đánh giá (Evaluation Framework) chuẩn mực phải phân biệt giữa 'Độ đầy đủ theo câu hỏi' và 'Độ đầy đủ theo bằng chứng có thể kiểm chứng'. Phạt một câu trả lời vì nó từ chối bịa đặt thông tin ngoài ngữ liệu là một lỗi phương pháp luận nghiêm trọng, phá hủy tính an toàn của hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic AI Safety Guidelines &amp; Press et al. (2022): 'Measuring Hallucination and Honest Abstention in Grounded QA'</t>
         </is>
       </c>
     </row>
@@ -746,10 +778,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra câu hỏi, đáp án kỳ vọng và bằng chứng hỗ trợ đáp án đó.
-Phân tích theo nguyên lý thiết kế: Kiểm tra câu hỏi, đáp án kỳ vọng và bằng chứng hỗ trợ đáp án đó.</t>
+- [Đánh giá tập câu hỏi không đạt chuẩn] (1.5 điểm): Chỉ ra nguy cơ đáp án chuẩn ảo giác và thiếu liên kết với corpus thực tế làm hỏng kết quả test.
+- [Quy trình 4 bước nghiệm thu chặt chẽ] (2.0 điểm): Thiết kế quy trình chuẩn: sinh gắn với chunk nguồn, lọc tự động bằng NLI entailment, thẩm định mẫu bởi con người, và đóng băng phiên bản.
+- [Bảo toàn liên kết Source Chunk ID] (0.5 điểm): Nhấn mạnh mỗi câu hỏi phải gắn kèm expected chunk ID để đo lường retrieval.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá chất lượng tập câu hỏi tổng hợp (Synthetic Dataset Evaluation):
+- Đánh giá: **TẬP CÂU HỎI HIỆN TẠI HOÀN TOÀN KHÔNG ĐỦ TIÊU CHUẨN NGHIỆM THU (Unqualified Synthetic Dataset)**.
+- Phân tích nguy cơ: Việc dùng LLM sinh 500 câu hỏi mà không đối chiếu tài liệu nguồn sẽ tạo ra hai thảm họa kiểm thử:
+  (a) **Ảo giác đề bài (Hallucinated Gold Answers)**: Đáp án chuẩn không có trong corpus nhưng lại được dùng làm thước đo chấm điểm, dẫn đến việc hệ thống RAG thực tế hoạt động đúng (từ chối hoặc trả lời theo nguồn) lại bị chấm là 'sai';
+  (b) **Thiếu liên kết căn cứ (Unlinked Ground Truth)**: Câu hỏi không neo giữ vào `chunk_id` cụ thể trong kho ngữ liệu, khiến không thể tính toán được các chỉ số truy xuất khách quan (Context Recall, MRR).
+2. Thiết kế Quy trình Nghiệm thu và Làm sạch Bộ kiểm thử (Testset Acceptance Protocol):
+- **Bước 1: Lọc ngược bằng chứng (Corpus-Grounded Filtering)**:
+  Mỗi câu hỏi tổng hợp bắt buộc phải được sinh ra từ một đoạn văn bản cụ thể trong corpus: `Question = Generator(Chunk_C)`. Lưu giữ liên kết bắt buộc: `{query, source_chunk_id, gold_answer_facts}`.
+- **Bước 2: Kiểm tra đối chiếu tự động (Automated Verification Filter)**:
+  Chạy một mô hình Verifier độc lập để xác minh: Câu trả lời chuẩn có được suy diễn trực tiếp 100% từ `source_chunk_id` hay không (`is_entailed == True`). Tự động loại bỏ bất kỳ cặp QA nào không đạt.
+- **Bước 3: Thẩm định chuyên gia con người (Human-in-the-loop Sample Audit)**:
+  Chuyên gia thẩm định ngẫu nhiên ít nhất 10-20% bộ câu hỏi để xác nhận tính tự nhiên, không bị thiên lệch từ vựng và phù hợp với thực tế.
+- **Bước 4: Đóng băng phiên bản (Freeze Version)**: Khóa bộ 500 câu hỏi thành `testset_v1.0.json` có mã băm SHA-256.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp sinh dữ liệu tổng hợp (Synthetic Test Generation như trong Ragas) chỉ có giá trị khi tuân thủ nguyên tắc 'Grounding-First': câu hỏi và câu trả lời phải được tạo ra từ chính các nút tài liệu thực tế của corpus. Dữ liệu tổng hợp trôi nổi không kiểm chứng sẽ làm hỏng hoàn toàn độ tin cậy của các báo cáo hồi quy.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Es et al. (2023): 'Ragas: Automated Evaluation of Retrieval Augmented Generation' - Testset Generation Module</t>
         </is>
       </c>
     </row>
@@ -832,10 +881,26 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách phép kiểm tra chính xác bằng code khỏi phần đánh giá ngữ nghĩa bằng LLM judge.
-Phân tích theo nguyên lý thiết kế: Tách phép kiểm tra chính xác bằng code khỏi phần đánh giá ngữ nghĩa bằng LLM judge.</t>
+- [Chỉ rõ 3 lỗi của hệ thống hiện tại] (1.5 điểm): Nhận diện đúng lỗi dùng LLM cho exact check, lỗi không phiên bản hóa model gây trôi điểm, và ngộ nhận điểm LLM là ground truth.
+- [Tách tầng kiểm tra bằng Code tất định] (1.5 điểm): Đưa các phép kiểm citation, regex, url sang chạy bằng hàm Python thuần nhanh và chính xác 100%.
+- [Chuẩn hóa LLM Judge cho đánh giá ngữ nghĩa] (1.0 điểm): Cố định model snapshot, zero temperature, seed cố định, rubric few-shot và reasoning chain.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra các lỗi nghiêm trọng trong hệ thống chấm hiện tại (Flaw Identification):
+- **Lỗi 1: Dùng LLM Judge cho các phép kiểm tra chính xác mang tính tất định (Using LLM for Deterministic Exact Checks)**:
+  Việc đối chiếu citation (kiểm tra xem ID có tồn tại trong context không, link có 404 không, định dạng ID có đúng regex không) là một bài toán logic nhị phân tất định (Deterministic Logic). Dùng LLM để làm việc này vừa tốn kém tiền bạc, độ trễ cao, vừa thiếu chính xác do LLM dễ bị ảo giác và không ổn định.
+- **Lỗi 2: Sử dụng LLM Judge không có phiên bản (Unpinned / Non-versioned Model)**:
+  Sử dụng một model endpoint không cố định phiên bản (ví dụ dùng model alias `gpt-4` thay vì `gpt-4-0613` hoặc không cố định seed/temperature) khiến điểm số đánh giá bị trôi dạt theo thời gian (Model Drift). Hôm nay chấm 4.5/5, ngày mai nhà cung cấp cập nhật trọng số ngầm có thể chấm 3.5/5 trên cùng một câu trả lời, phá hủy hoàn toàn khả năng so sánh hồi quy.
+- **Lỗi 3: Coi điểm LLM Judge là Ground-Truth tuyệt đối**: Điểm LLM Judge chỉ là ước lượng gần đúng, không thể thay thế hoàn toàn ground-truth của chuyên gia.
+2. Thiết kế lại Hệ thống Chấm điểm Đa tầng (Redesigned Hybrid Evaluation System):
+- **Tầng 1: Kiểm tra Tất định bằng Mã nguồn (Deterministic Code-based Checks - Hard Gate)**:
+  + Dùng hàm Python thuần kiểm tra: Độ dài câu trả lời, Regex định dạng JSON/Citation, kiểm tra ID trích dẫn có nằm trong context không, kiểm tra liên kết URL bằng HTTP HEAD request.
+- **Tầng 2: Đánh giá Ngữ nghĩa bằng LLM Judge Đóng băng (Version-Pinned LLM Judge)**:
+  + Cố định phiên bản mô hình cụ thể (Pinned Snapshot Model ID), đặt `temperature = 0.0`, `seed = 42`.
+  + Cung cấp Rubric chi tiết với các tiêu chí chấm điểm từng nấc (Few-shot Examples) và yêu cầu xuất ra chuỗi suy luận trước khi cho điểm số (Chain-of-Thought Reasoning).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc phân tầng đánh giá: 'Code for syntax and exact matches, LLM for semantic reasoning'. Sử dụng đúng công cụ cho đúng bài toán và phiên bản hóa nghiêm ngặt mô hình đánh giá là tiêu chuẩn bắt buộc để hệ thống đánh giá tự động đạt tính ổn định và khả năng tái lập trong môi trường sản xuất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Zheng et al. (2023): 'Judging LLM-as-a-Judge with MT-Bench and Chatbot Arena' (NeurIPS 2023) &amp; Ragas Judge Guidelines</t>
         </is>
       </c>
     </row>
@@ -914,10 +979,28 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc mẫu metric rồi đối chiếu với các tầng retrieval, augmentation và generation.
-Phân tích theo nguyên lý thiết kế: Đọc mẫu metric rồi đối chiếu với các tầng retrieval, augmentation và generation.</t>
+- [Chẩn đoán chính xác lỗi ở tầng Generation] (1.5 điểm): Phân tích scorecard: Retrieval hoàn hảo (Recall/Precision cao), lỗi duy nhất là Faithfulness thấp (ảo giác ở bước sinh văn bản).
+- [Cấm thay đổi các tầng Retrieval/Augmentation] (1.0 điểm): Nhấn mạnh nguyên tắc giữ cố định toàn bộ các tham số retrieval đã hoạt động tốt.
+- [Thiết kế duy nhất 1 phép thử có mục tiêu] (1.5 điểm): Thắt chặt prompt grounding và hạ temperature=0.0 ở tầng generator, đo lường sự phục hồi của Faithfulness.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán Scorecard và Định vị Tầng lỗi (Scorecard Metric Diagnosis):
+- **Phân tích các chỉ số**:
+  + `Recall cao` (Context Recall): Tầng Retrieval đã thu hồi đầy đủ tất cả các dữ kiện cần thiết từ kho tài liệu.
+  + `Precision cao` (Context Precision): Các chunk đưa vào context đều liên quan cao, không bị tràn ngập nhiễu.
+  + `Relevance trung bình` (Answer Relevance): Câu trả lời đi vào chủ đề nhưng chưa thực sự sắc sảo hoặc có chi tiết thừa/thiếu tập trung.
+  + `Độ đầy đủ cao` (Answer Completeness): Câu trả lời cung cấp đầy đủ các khía cạnh thông tin.
+  + **`Độ bám bằng chứng THẤP` (Faithfulness / Groundedness is LOW)**: Đây chính là **ĐIỂM NGHẼN CỐT LÕI VÀ LỖI DUY NHẤT CẦN CAN THIỆP**! Mô hình đã tự ý bịa đặt thêm các chi tiết, con số hoặc suy diễn ngoài ngữ cảnh (Hallucination Defect).
+- **Kết luận tầng lỗi**: Tầng Retrieval và Augmentation hoạt động hoàn hảo! Lỗi nằm 100% ở **TẦNG TẠO SINH (Generation Layer)**.
+2. Lựa chọn Phép thử tiếp theo mà KHÔNG thay đổi mọi thành phần cùng lúc (Single-Variable Controlled Experiment):
+- **Tuyệt đối KHÔNG thay đổi**: Không đổi mô hình embedding, không đổi chunk size, không đổi top-k, không đổi reranker (vì retrieval đã đạt Recall và Precision cao).
+- **Phép thử duy nhất được chọn (Targeted Generation Experiment)**:
+  + Can thiệp vào System Prompt của Generator: Bổ sung chỉ thị bám sát nguyên văn (Strict Grounding Directive) và quy tắc từ chối bịa đặt: 'Chỉ sử dụng thông tin có trong ngữ cảnh. Tuyệt đối không thêm thắt số liệu ngoài tài liệu'.
+  + Đồng thời hạ nhiệt độ sinh văn bản về `temperature = 0.0`.
+- Phép đo xác minh: Đo lại Faithfulness trên cùng tập testset cố định. Kỳ vọng Faithfulness tăng vọt từ thấp lên &gt; 0.95 trong khi giữ nguyên Recall và Precision cao.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc chẩn đoán phân tầng RAG: Khi một scorecard cho thấy một metric đơn lẻ bị sụp đổ (Faithfulness thấp) trong khi các metric khác đều cao (Recall cao, Precision cao), nguyên nhân đã được cô lập hoàn toàn ở bước biến đổi ngữ cảnh thành câu trả lời (Tầng Generation). Thay đổi nhiều thành phần cùng lúc sẽ phá vỡ tính đối chứng và làm phức tạp hóa vấn đề.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+TruLens: 'Diagnosing the RAG Triad' &amp; Ragas: 'End-to-End Evaluation Scorecard Interpretation'</t>
         </is>
       </c>
     </row>
